--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Game\Git\TEngine_main\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB5F6B8-6D11-4B26-9DE2-4F16FE9591B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37A9F56-A6E2-47EB-8A16-258A4512C5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28815" yWindow="15" windowWidth="28770" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
   <si>
     <t>##var</t>
   </si>
@@ -140,6 +140,10 @@
   </si>
   <si>
     <t>位标记使用示例</t>
+  </si>
+  <si>
+    <t>##</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -157,6 +161,7 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -593,6 +598,9 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
@@ -616,6 +624,9 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
       <c r="H5" t="s">
         <v>23</v>
       </c>
@@ -630,6 +641,9 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
       <c r="H6" t="s">
         <v>26</v>
       </c>
@@ -644,6 +658,9 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
       <c r="H7" t="s">
         <v>29</v>
       </c>
@@ -658,6 +675,9 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
       <c r="B8" t="s">
         <v>32</v>
       </c>
@@ -675,6 +695,9 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
       <c r="H9" t="s">
         <v>34</v>
       </c>
@@ -683,6 +706,9 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>40</v>
+      </c>
       <c r="H10" t="s">
         <v>35</v>
       </c>
@@ -691,6 +717,9 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
       <c r="H11" t="s">
         <v>36</v>
       </c>
@@ -699,6 +728,9 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>40</v>
+      </c>
       <c r="H12" t="s">
         <v>37</v>
       </c>
